--- a/qa/relatorios/Consolidado_QA_Velodesk.xlsx
+++ b/qa/relatorios/Consolidado_QA_Velodesk.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="339">
   <si>
     <t>Data</t>
   </si>
@@ -69,6 +69,15 @@
     <t>Login de atendente: Login recusado: Credenciais inválidas. Sem login, nenhuma tela do CRM abre. • Contadores das filas: Sem sessão — o login falhou nesta rodada. • Criar ticket pela API de entrada: Criação de ticket recusada (status 401): Chave inbound ticket incorreta • Ticket criado aparece na busca por protocolo: Nenhum ticket de teste foi criado nesta rodada. • Proteção contra ticket duplicado: Nenhum ticket de teste foi criado nesta rodada. • Ticket novo entra na fila: Sem sessão de atendente para consultar as filas. • Volume de tickets criados: Nenhum ticket criado nas últimas 24h. Suspeita de entrada travada. • Anotação interna: Nenhum ticket de teste disponível. • Resposta pública ao cliente: Nenhum ticket de teste disponível. • Tabulação (árvore de motivos): Nenhum ticket de teste disponível. • Trava: finalizar sem responsável: Sem ticket auxiliar de teste nesta rodada. • Trava: finalizar sem tabulação: Sem ticket auxiliar de teste nesta rodada. • Finalizar ticket: Nenhum ticket de teste disponível. • Trava: mesclar com CPF divergente: São necessários dois tickets de teste e apenas um foi criado. • Mesclar dois tickets do mesmo cliente: São necessários dois tickets de teste e apenas um foi criado. • Ticket absorvido sai da fila: A mesclagem não aconteceu nesta rodada. • Registrar nota do cliente: Nenhum ticket de teste disponível. • Trava: nota inválida: Nenhum ticket de teste disponível. • Trava: avaliação não enviada: Sem ticket auxiliar sem pesquisa enviada para a checagem. • Nota não é sobrescrita: A nota não foi registrada nesta rodada. • E-mail do ticket de teste: Nenhum ticket de teste disponível. • Tickets parados como novos: 137 tickets parados em "novo" há mais de 24h — fila sem tratamento ou roleta parada. • Módulos do console: Sem sessão de atendente. • "Meu dia" (cockpit do agente): Sem sessão de atendente — o login pela API falhou nesta rodada. • Fila de atendimento: Sem sessão de atendente — o login pela API falhou nesta rodada. • Ticket aberto: Sem sessão de atendente — o login pela API falhou nesta rodada.</t>
   </si>
   <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>18s</t>
+  </si>
+  <si>
+    <t>Volume de tickets criados: Nenhum ticket criado nas últimas 24h. Suspeita de entrada travada. • Anotação interna: A API aceitou a anotação, mas ela não apareceu no histórico do ticket. • Finalizar ticket: A API aceitou, mas o ticket ficou com status "" em vez de "resolvido". • Mesclar dois tickets do mesmo cliente: A API respondeu com sucesso, mas o ticket ativo não ficou marcado como superior da mesclagem. • Ticket absorvido sai da fila: O ticket absorvido não ficou marcado como inferior da mesclagem — ele continuaria nas filas. • Registrar nota do cliente: Erro inesperado durante a checagem: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586264 não encontrado. • Nota não é sobrescrita: A nota não foi registrada nesta rodada. • Tickets parados como novos: 137 tickets parados em "novo" há mais de 24h — fila sem tratamento ou roleta parada. • Tickets de teste que não foram encerrados: 2609140132: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586264 não encontrado. | 2609140133: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586280 não encontrado. | 2609140134: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586290 não encontrado.</t>
+  </si>
+  <si>
     <t>Agente</t>
   </si>
   <si>
@@ -792,6 +801,141 @@
     <t>Verifique com responsáveis alterações recentes no console para confirmar se módulos estão desligados intencionalmente antes de registrar como falha.</t>
   </si>
   <si>
+    <t>Erro inesperado durante a checagem: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586264 não encontrado.</t>
+  </si>
+  <si>
+    <t>Cheque POST /api/csat e a gravação do subdocumento csat (nota, respondido, respondidoEm) para garantir que o ticket existe e o CSAT é registrado.</t>
+  </si>
+  <si>
+    <t>2609140132</t>
+  </si>
+  <si>
+    <t>Trava funcionando: nota fora de 1 a 5 recusada ("Nota inválida (esperado inteiro de 1 a 5).").</t>
+  </si>
+  <si>
+    <t>2609140134</t>
+  </si>
+  <si>
+    <t>Trava funcionando: protocolo sem pesquisa enviada não aceita nota.</t>
+  </si>
+  <si>
+    <t>Restaure a checagem de csat.respondido para garantir idempotência e bloquear sobrescrita indevida da nota do cliente.</t>
+  </si>
+  <si>
+    <t>Inicie pela confirmação dos casos S03 e E06 para verificar transporte de e-mail e ativação dos modelos, pois zero disparos indicam configuração ou transporte parado.</t>
+  </si>
+  <si>
+    <t>O ticket de teste não registrou nenhum e-mail enviado. Pode ser modelo de gatilho inativo ou transporte de e-mail indisponível (ver casos S03 e E02).</t>
+  </si>
+  <si>
+    <t>Verifique a ativação do modelo com gatilho para abertura e a disponibilidade do transporte de e-mail para garantir registro de envio no ticket de teste.</t>
+  </si>
+  <si>
+    <t>IA encontrou 4 ponto(s) de atenção — "Repescagem da satisfação": O texto usa primeira pessoa singular e pede avaliação, mas a assinatura é do time; além disso, o convite fixo para responder e-mail conflita com pedido de clique em link. | "Validação da alteração de cadastro": O texto usa primeira pessoa singular ('agradeço', 'estou aqui') e fala de 'eu', mas a assinatura é do time, causando desconexão. | "Encerramento s/CSAT": O corpo usa primeira pessoa singular ('fico à disposição'), desarmonizando com assinatura coletiva do time. | "Encerramento mais satisfação": O texto pede resposta via clique para avaliação (CSAT), contradizendo o convite automático para responder o e-mail.</t>
+  </si>
+  <si>
+    <t>Revise na aba Emails de Saída os modelos apontados na observação, ajustando textos para evitar conflito entre pedido de resposta e assinatura padrão do time.</t>
+  </si>
+  <si>
+    <t>2609140133</t>
+  </si>
+  <si>
+    <t>Trava funcionando: o sistema recusou com "Atribua um responsável real ao ticket antes de encerrá-lo.".</t>
+  </si>
+  <si>
+    <t>Trava funcionando: o sistema recusou com "Preencha a tabulação antes de enviar: Produto, Tipo.".</t>
+  </si>
+  <si>
+    <t>A API aceitou, mas o ticket ficou com status "" em vez de "resolvido".</t>
+  </si>
+  <si>
+    <t>Confirme a transição de status na rota POST /api/tickets/:id/commit e a correta empilhamento em registro[] com responsável e tabulação, para evitar status vazio.</t>
+  </si>
+  <si>
+    <t>2609140134 (ativo) / 2609140133 (inativo)</t>
+  </si>
+  <si>
+    <t>A API respondeu com sucesso, mas o ticket ativo não ficou marcado como superior da mesclagem.</t>
+  </si>
+  <si>
+    <t>Confira POST /api/ticket-fusao para validar CPF com 11 dígitos, unicidade do cliente e que tickets não estejam fechados ou absorvidos para marcar mesclagem corretamente.</t>
+  </si>
+  <si>
+    <t>O ticket absorvido não ficou marcado como inferior da mesclagem — ele continuaria nas filas.</t>
+  </si>
+  <si>
+    <t>Verifique a gravação de fusao.hierarquia e o filtro excludeFusaoAbsorvidosFilter para que o ticket absorvido seja marcado como inferior e removido das filas.</t>
+  </si>
+  <si>
+    <t>Trava funcionando: o sistema recusou com "O ticket ativo não pertence ao CPF informado.".</t>
+  </si>
+  <si>
+    <t>A API aceitou a anotação, mas ela não apareceu no histórico do ticket.</t>
+  </si>
+  <si>
+    <t>Verifique a rota POST /api/tickets/:id/messages e a gravação no campo registro[].anotacaoInterna para garantir a persistência no histórico.</t>
+  </si>
+  <si>
+    <t>Falha conhecida</t>
+  </si>
+  <si>
+    <t>A resposta foi aceita pela API, mas não ficou gravada na conversa do ticket. | Já mapeado: BUG CRÍTICO já mapeado no consolidado de 21/08: resposta pública pelo Compose não conclui o envio.</t>
+  </si>
+  <si>
+    <t>Acompanhe a correção do bug crítico já mapeado no Compose, monitorando o commit e notifyAgentReplyAsync sem reportar como novo problema.</t>
+  </si>
+  <si>
+    <t>Nenhuma tabulação foi gravada no ticket. | Já mapeado: Falha conhecida do consolidado de 21/08: árvore de motivos não é preenchida automaticamente pela sugestão de IA.</t>
+  </si>
+  <si>
+    <t>Confira a ativação da árvore de motivos (GET /api/tabulation) e se a sugestão de IA está preenchendo os campos antes do commit para garantir tabulação.</t>
+  </si>
+  <si>
+    <t>Implemente primeiro a função de encaminhamento na tela e a rota de API correspondente; sem isso, o caso não é testável nem monitorável.</t>
+  </si>
+  <si>
+    <t>API no ar, respondeu em 98 ms.</t>
+  </si>
+  <si>
+    <t>Login do atendente "QA Teste" funcionou em 41 ms.</t>
+  </si>
+  <si>
+    <t>Contadores respondendo: 1381 tickets no total, 168 em aberto, 7 atendentes.</t>
+  </si>
+  <si>
+    <t>Ticket criado em 217 ms — protocolo 2609140132, canal .</t>
+  </si>
+  <si>
+    <t>Ticket 2609140132 encontrado pela busca por protocolo, com status "novo".</t>
+  </si>
+  <si>
+    <t>Reenvio do mesmo pedido não criou ticket duplicado (devolveu o protocolo original).</t>
+  </si>
+  <si>
+    <t>Fila de novos com 46 ticket(s).</t>
+  </si>
+  <si>
+    <t>Confira as sondas de entrada (e-mail, telefonia, app) uma a uma para identificar bloqueios, pois volume baixo indica entrada travada, impactando a criação de tickets.</t>
+  </si>
+  <si>
+    <t>Cockpit abriu com o bloco "Meu dia" e 5 indicador(es).</t>
+  </si>
+  <si>
+    <t>Fila de atendimento abriu com as 5 caixas e seus contadores.</t>
+  </si>
+  <si>
+    <t>Ticket 2609140132 abriu com as abas Conversa / Notas / Eventos / Consultas.</t>
+  </si>
+  <si>
+    <t>Confirme se ASSIGNMENT_ROUTER_ENABLED está ativo e revise a distribuição por atendente para evitar tickets parados em "novo" há mais de 24h.</t>
+  </si>
+  <si>
+    <t>Módulo(s) fora do ar ou em revisão: Seguro (off).</t>
+  </si>
+  <si>
+    <t>Confirme com a equipe responsável se o módulo Seguro está desligado ou em revisão, para evitar tratar como incidente indevido.</t>
+  </si>
+  <si>
     <t>Indicador</t>
   </si>
   <si>
@@ -871,13 +1015,28 @@
   </si>
   <si>
     <t>Tickets em "novo" há mais de 24h</t>
+  </si>
+  <si>
+    <t>Tickets no total</t>
+  </si>
+  <si>
+    <t>Tickets resolvidos (acumulado)</t>
+  </si>
+  <si>
+    <t>Tickets em aberto agora</t>
+  </si>
+  <si>
+    <t>Atendentes cadastrados</t>
+  </si>
+  <si>
+    <t>Tickets na fila "Novos"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -892,6 +1051,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -944,7 +1107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -965,6 +1128,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1306,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1398,16 +1564,54 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2">
+        <v>49</v>
+      </c>
+      <c r="F3" s="2">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2">
+        <v>7</v>
+      </c>
+      <c r="I3" s="2">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1436,37 +1640,37 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1480,37 +1684,37 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1524,37 +1728,37 @@
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="N3" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1568,37 +1772,37 @@
         <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1612,37 +1816,37 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1656,37 +1860,37 @@
         <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1700,37 +1904,37 @@
         <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1744,37 +1948,37 @@
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1788,37 +1992,37 @@
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1832,37 +2036,37 @@
         <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1876,37 +2080,37 @@
         <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1920,37 +2124,37 @@
         <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1964,37 +2168,37 @@
         <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2008,37 +2212,37 @@
         <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2052,37 +2256,37 @@
         <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2096,37 +2300,37 @@
         <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2140,37 +2344,37 @@
         <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2184,37 +2388,37 @@
         <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="N18" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2228,37 +2432,37 @@
         <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2272,37 +2476,37 @@
         <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2316,37 +2520,37 @@
         <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2360,37 +2564,37 @@
         <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2404,37 +2608,37 @@
         <v>14</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2448,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2492,37 +2696,37 @@
         <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2536,37 +2740,37 @@
         <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2580,37 +2784,37 @@
         <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2624,37 +2828,37 @@
         <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2668,37 +2872,37 @@
         <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2712,37 +2916,37 @@
         <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2756,37 +2960,37 @@
         <v>14</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2800,37 +3004,37 @@
         <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2844,37 +3048,37 @@
         <v>14</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2888,37 +3092,37 @@
         <v>14</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2932,37 +3136,37 @@
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2976,37 +3180,37 @@
         <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3020,37 +3224,37 @@
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3064,37 +3268,37 @@
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M38" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="N38" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3108,37 +3312,37 @@
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3152,37 +3356,37 @@
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3196,37 +3400,37 @@
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3240,37 +3444,37 @@
         <v>14</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3284,37 +3488,37 @@
         <v>14</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3328,37 +3532,37 @@
         <v>14</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M44" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="N44" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3372,37 +3576,37 @@
         <v>14</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3416,37 +3620,37 @@
         <v>14</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3460,37 +3664,37 @@
         <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3504,37 +3708,37 @@
         <v>14</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3548,37 +3752,37 @@
         <v>14</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3592,49 +3796,2222 @@
         <v>14</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L52" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="M52" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L75" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L76" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L86" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G94" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="H94" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H98" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="I98" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M98" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M50" s="2" t="s">
+      <c r="N98" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="N50" s="2" t="s">
+      <c r="G99" s="2" t="s">
         <v>258</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
+  <hyperlinks>
+    <hyperlink ref="L52" r:id="rId1"/>
+    <hyperlink ref="L53" r:id="rId2"/>
+    <hyperlink ref="L61" r:id="rId3"/>
+    <hyperlink ref="L66" r:id="rId4"/>
+    <hyperlink ref="L67" r:id="rId5"/>
+    <hyperlink ref="L68" r:id="rId6"/>
+    <hyperlink ref="L71" r:id="rId7"/>
+    <hyperlink ref="L72" r:id="rId8"/>
+    <hyperlink ref="L73" r:id="rId9"/>
+    <hyperlink ref="L75" r:id="rId10"/>
+    <hyperlink ref="L76" r:id="rId11"/>
+    <hyperlink ref="L77" r:id="rId12"/>
+    <hyperlink ref="L85" r:id="rId13"/>
+    <hyperlink ref="L86" r:id="rId14"/>
+    <hyperlink ref="L87" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3653,16 +6030,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>308</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3673,16 +6050,16 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>262</v>
+        <v>310</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3693,16 +6070,16 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3713,16 +6090,16 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>267</v>
+        <v>315</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3733,16 +6110,16 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>268</v>
+        <v>316</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3753,16 +6130,16 @@
         <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3773,16 +6150,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="D7" s="2">
         <v>627</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3793,16 +6170,16 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="D8" s="2">
         <v>60</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3813,16 +6190,16 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3833,16 +6210,16 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3853,16 +6230,16 @@
         <v>13</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3873,16 +6250,16 @@
         <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3893,16 +6270,16 @@
         <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="D13" s="2">
         <v>114</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3913,16 +6290,16 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3933,16 +6310,16 @@
         <v>13</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>281</v>
+        <v>329</v>
       </c>
       <c r="D15" s="2">
         <v>12</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3953,16 +6330,16 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3973,16 +6350,16 @@
         <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3993,16 +6370,16 @@
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="D18" s="2">
         <v>137</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4013,21 +6390,481 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1381</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1136</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D22" s="2">
+        <v>168</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D23" s="2">
+        <v>7</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" s="2">
+        <v>46</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D30" s="2">
+        <v>627</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D31" s="2">
+        <v>60</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D36" s="2">
+        <v>114</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D38" s="2">
+        <v>12</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D41" s="2">
+        <v>137</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/qa/relatorios/Consolidado_QA_Velodesk.xlsx
+++ b/qa/relatorios/Consolidado_QA_Velodesk.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="371">
   <si>
     <t>Data</t>
   </si>
@@ -78,6 +78,18 @@
     <t>Volume de tickets criados: Nenhum ticket criado nas últimas 24h. Suspeita de entrada travada. • Anotação interna: A API aceitou a anotação, mas ela não apareceu no histórico do ticket. • Finalizar ticket: A API aceitou, mas o ticket ficou com status "" em vez de "resolvido". • Mesclar dois tickets do mesmo cliente: A API respondeu com sucesso, mas o ticket ativo não ficou marcado como superior da mesclagem. • Ticket absorvido sai da fila: O ticket absorvido não ficou marcado como inferior da mesclagem — ele continuaria nas filas. • Registrar nota do cliente: Erro inesperado durante a checagem: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586264 não encontrado. • Nota não é sobrescrita: A nota não foi registrada nesta rodada. • Tickets parados como novos: 137 tickets parados em "novo" há mais de 24h — fila sem tratamento ou roleta parada. • Tickets de teste que não foram encerrados: 2609140132: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586264 não encontrado. | 2609140133: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586280 não encontrado. | 2609140134: TRAVA DE SEGURANÇA: Ticket 6aa830c4c1673f74eb586290 não encontrado.</t>
   </si>
   <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>Tarde (15h)</t>
+  </si>
+  <si>
+    <t>21s</t>
+  </si>
+  <si>
+    <t>Volume de tickets criados: Nenhum ticket criado nas últimas 24h. Suspeita de entrada travada. • Anotação interna: A API aceitou a anotação, mas ela não apareceu no histórico do ticket. • Finalizar ticket: A API aceitou, mas o ticket ficou com status "" em vez de "resolvido". • Mesclar dois tickets do mesmo cliente: A API respondeu com sucesso, mas o ticket ativo não ficou marcado como superior da mesclagem. • Ticket absorvido sai da fila: O ticket absorvido não ficou marcado como inferior da mesclagem — ele continuaria nas filas. • Registrar nota do cliente: Erro inesperado durante a checagem: TRAVA DE SEGURANÇA: Ticket 6aa8377ec1673f74eb58807b não encontrado. • Nota não é sobrescrita: A nota não foi registrada nesta rodada. • Tickets parados como novos: 137 tickets parados em "novo" há mais de 24h — fila sem tratamento ou roleta parada. • Tickets de teste que não foram encerrados: 2609140138: TRAVA DE SEGURANÇA: Ticket 6aa8377ec1673f74eb58807b não encontrado. | 2609140139: TRAVA DE SEGURANÇA: Ticket 6aa8377fc1673f74eb588098 não encontrado. | 2609140140: TRAVA DE SEGURANÇA: Ticket 6aa8377fc1673f74eb5880aa não encontrado.</t>
+  </si>
+  <si>
     <t>Agente</t>
   </si>
   <si>
@@ -934,6 +946,90 @@
   </si>
   <si>
     <t>Confirme com a equipe responsável se o módulo Seguro está desligado ou em revisão, para evitar tratar como incidente indevido.</t>
+  </si>
+  <si>
+    <t>Erro inesperado durante a checagem: TRAVA DE SEGURANÇA: Ticket 6aa8377ec1673f74eb58807b não encontrado.</t>
+  </si>
+  <si>
+    <t>Verifique POST /api/csat e a gravação do subdocumento csat, pois a ausência do ticket indica problema na identificação que compromete relatórios de satisfação.</t>
+  </si>
+  <si>
+    <t>2609140138</t>
+  </si>
+  <si>
+    <t>2609140140</t>
+  </si>
+  <si>
+    <t>Restaure a checagem de csat.respondido para garantir idempotência e evitar sobrescrição da nota do cliente, imprescindível para integridade da avaliação.</t>
+  </si>
+  <si>
+    <t>Comece pelos casos S03 e E06 revisando o transporte de e-mail e a ativação dos modelos para resolver ausência de e-mails automáticos por gatilho.</t>
+  </si>
+  <si>
+    <t>Confirme existência de modelo com gatilho para abertura de atendimento e se o transporte de e-mail está operacional para garantir registro no histórico do ticket de teste.</t>
+  </si>
+  <si>
+    <t>IA encontrou 10 ponto(s) de atenção — "Repescagem da satisfação": Texto em primeira pessoa 'ainda não recebi' destoa da assinatura institucional em nome de time. | "Portabilidade da chave PIX ( sem pendência )": Tipo CSAT incompatível com o corpo informativo; espera ação sem avaliação ou pesquisa. | "Validação da alteração de cadastro": Uso de primeira pessoa 'Agradeço' e 'eu dou andamento' contrasta com assinatura em nome do time. | "Encerramento s/CSAT": Uso de primeira pessoa 'fico à disposição' destoa da assinatura institucional em nome de time. | "Pós - Exclusão chave pix 2026( com pendência )": Tipo CSAT usado, mas corpo é apenas informativo; existe contradição na ação esperada. | "Encerramento Celcoin - Pix excluído.": Tipo CSAT não condiz com texto apenas informativo e sem pedido de avaliação. | "Pré - Liberação chave pix - Quebra contratual": Tipo CSAT não coerente com o texto, que não pede avaliação nem resposta. | "Abertura de protocolo de atendimento": Instrução 'Para responder, utilize este e-mail' soa repetitiva e confusa junto do convite fixo. | "Abertura de protocolo de atendimento - e-mail": Instrução para responder usando protocolo soa desnecessária dado o convite fixo para resposta simples. | "Encerramento mais satisfação": CSAT pede clique na avaliação, mas convite fixo sugere responder e-mail — instruções conflitantes.</t>
+  </si>
+  <si>
+    <t>Revise os textos na aba Emails de Saída, ajustando saudações e corpo para evitar incoerência com a assinatura automática e garantir clareza na comunicação.</t>
+  </si>
+  <si>
+    <t>2609140139</t>
+  </si>
+  <si>
+    <t>Confirme na rota POST /api/tickets/:id/commit se o status está corretamente alterado para 'resolvido' e a transição está registrada no histórico com responsável e tabulação.</t>
+  </si>
+  <si>
+    <t>2609140140 (ativo) / 2609140139 (inativo)</t>
+  </si>
+  <si>
+    <t>Cheque no POST /api/ticket-fusao a validação do CPF, consistência do cliente entre tickets e status para assegurar a marcação correta do ticket ativo como superior.</t>
+  </si>
+  <si>
+    <t>Confira gravação de fusao.hierarquia e o filtro excludeFusaoAbsorvidosFilter para garantir que o ticket absorvido seja marcado como inferior e não apareça nas filas.</t>
+  </si>
+  <si>
+    <t>Verifique a rota POST /api/tickets/:id/messages e a gravação do campo registro[].anotacaoInterna para garantir que anotações sejam persistidas no histórico.</t>
+  </si>
+  <si>
+    <t>Acompanhe as correções do bug crítico já mapeado no Compose referente à resposta pública para evitar retrabalho na resolução.</t>
+  </si>
+  <si>
+    <t>Verifique a ativação da árvore de motivos via GET /api/tabulation e a integração da sugestão IA para garantir o preenchimento correto da tabulação.</t>
+  </si>
+  <si>
+    <t>Para testar esta funcionalidade, é necessário que a função de encaminhamento esteja implementada e disponível tanto na interface quanto via API.</t>
+  </si>
+  <si>
+    <t>API no ar, respondeu em 122 ms.</t>
+  </si>
+  <si>
+    <t>Login do atendente "QA Teste" funcionou em 80 ms.</t>
+  </si>
+  <si>
+    <t>Contadores respondendo: 1387 tickets no total, 169 em aberto, 7 atendentes.</t>
+  </si>
+  <si>
+    <t>Ticket criado em 290 ms — protocolo 2609140138, canal .</t>
+  </si>
+  <si>
+    <t>Ticket 2609140138 encontrado pela busca por protocolo, com status "novo".</t>
+  </si>
+  <si>
+    <t>Fila de novos com 48 ticket(s).</t>
+  </si>
+  <si>
+    <t>Confira as sondas de entrada (e-mail, telefonia, app) para identificar travamento, pois impacto direto na geração de novos tickets e no fluxo de atendimento.</t>
+  </si>
+  <si>
+    <t>Ticket 2609140138 abriu com as abas Conversa / Notas / Eventos / Consultas.</t>
+  </si>
+  <si>
+    <t>Confira configuração ASSIGNMENT_ROUTER_ENABLED e a distribuição das filas por atendente para evitar tickets parados em status 'novo' por falha na roleta.</t>
+  </si>
+  <si>
+    <t>Confirme com o responsável as razões do módulo Seguro estar desligado ou em revisão antes de tratá-lo como falha operacional.</t>
   </si>
   <si>
     <t>Indicador</t>
@@ -1472,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1602,6 +1698,44 @@
         <v>20</v>
       </c>
     </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2">
+        <v>49</v>
+      </c>
+      <c r="F4" s="2">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2">
+        <v>7</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1611,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1640,37 +1774,37 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1684,37 +1818,37 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1728,37 +1862,37 @@
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="N3" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1772,37 +1906,37 @@
         <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1816,37 +1950,37 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1860,37 +1994,37 @@
         <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1904,37 +2038,37 @@
         <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1948,37 +2082,37 @@
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1992,37 +2126,37 @@
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2036,37 +2170,37 @@
         <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2080,37 +2214,37 @@
         <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2124,37 +2258,37 @@
         <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2168,37 +2302,37 @@
         <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2212,37 +2346,37 @@
         <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2256,37 +2390,37 @@
         <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2300,37 +2434,37 @@
         <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2344,37 +2478,37 @@
         <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2388,37 +2522,37 @@
         <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="N18" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2432,37 +2566,37 @@
         <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2476,37 +2610,37 @@
         <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2520,37 +2654,37 @@
         <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2564,37 +2698,37 @@
         <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2608,37 +2742,37 @@
         <v>14</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2652,37 +2786,37 @@
         <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2696,37 +2830,37 @@
         <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2740,37 +2874,37 @@
         <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2784,37 +2918,37 @@
         <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2828,37 +2962,37 @@
         <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2872,37 +3006,37 @@
         <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2916,37 +3050,37 @@
         <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2960,37 +3094,37 @@
         <v>14</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3004,37 +3138,37 @@
         <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3048,37 +3182,37 @@
         <v>14</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3092,37 +3226,37 @@
         <v>14</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3136,37 +3270,37 @@
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3180,37 +3314,37 @@
         <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3224,37 +3358,37 @@
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3268,37 +3402,37 @@
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H38" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M38" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="N38" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3312,37 +3446,37 @@
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3356,37 +3490,37 @@
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3400,37 +3534,37 @@
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3444,37 +3578,37 @@
         <v>14</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3488,37 +3622,37 @@
         <v>14</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3532,37 +3666,37 @@
         <v>14</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H44" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M44" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="N44" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3576,37 +3710,37 @@
         <v>14</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3620,37 +3754,37 @@
         <v>14</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3664,37 +3798,37 @@
         <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3708,37 +3842,37 @@
         <v>14</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3752,37 +3886,37 @@
         <v>14</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3796,37 +3930,37 @@
         <v>14</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3840,37 +3974,37 @@
         <v>14</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3884,37 +4018,37 @@
         <v>14</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="L52" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="L52" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="M52" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3928,37 +4062,37 @@
         <v>14</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="L53" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="L53" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="M53" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3972,37 +4106,37 @@
         <v>14</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4016,37 +4150,37 @@
         <v>14</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4060,37 +4194,37 @@
         <v>14</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4104,37 +4238,37 @@
         <v>14</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4148,37 +4282,37 @@
         <v>14</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4192,37 +4326,37 @@
         <v>14</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4236,37 +4370,37 @@
         <v>14</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4280,37 +4414,37 @@
         <v>14</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4324,37 +4458,37 @@
         <v>14</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4368,37 +4502,37 @@
         <v>14</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4412,37 +4546,37 @@
         <v>14</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4456,37 +4590,37 @@
         <v>14</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4500,37 +4634,37 @@
         <v>14</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4544,37 +4678,37 @@
         <v>14</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4588,37 +4722,37 @@
         <v>14</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4632,37 +4766,37 @@
         <v>14</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4676,37 +4810,37 @@
         <v>14</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4720,37 +4854,37 @@
         <v>14</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4764,37 +4898,37 @@
         <v>14</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4808,37 +4942,37 @@
         <v>14</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4852,37 +4986,37 @@
         <v>14</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4896,37 +5030,37 @@
         <v>14</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4940,37 +5074,37 @@
         <v>14</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4984,37 +5118,37 @@
         <v>14</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5028,37 +5162,37 @@
         <v>14</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5072,37 +5206,37 @@
         <v>14</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5116,37 +5250,37 @@
         <v>14</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5160,37 +5294,37 @@
         <v>14</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5204,37 +5338,37 @@
         <v>14</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5248,37 +5382,37 @@
         <v>14</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5292,37 +5426,37 @@
         <v>14</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5336,37 +5470,37 @@
         <v>14</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5380,37 +5514,37 @@
         <v>14</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5424,37 +5558,37 @@
         <v>14</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5468,37 +5602,37 @@
         <v>14</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5512,37 +5646,37 @@
         <v>14</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5556,37 +5690,37 @@
         <v>14</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5600,37 +5734,37 @@
         <v>14</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5644,37 +5778,37 @@
         <v>14</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5688,37 +5822,37 @@
         <v>14</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5732,37 +5866,37 @@
         <v>14</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5776,37 +5910,37 @@
         <v>14</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5820,37 +5954,37 @@
         <v>14</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5864,37 +5998,37 @@
         <v>14</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5908,37 +6042,37 @@
         <v>14</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5952,37 +6086,2193 @@
         <v>14</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E99" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N110" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N111" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N112" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="L116" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="N116" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M117" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="N117" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N118" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="L120" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="L121" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="L122" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="N122" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N123" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L124" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="N124" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L125" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L126" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I127" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N128" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I129" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N129" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M130" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="N130" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="N131" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N132" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I133" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N133" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I134" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L134" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="N134" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I135" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L135" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L136" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="N136" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I137" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L137" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M137" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="N137" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="N138" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="N139" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I141" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="N141" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M142" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="N142" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F143" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="G143" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I143" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M143" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N143" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M144" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="N144" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M145" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="N145" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I146" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="N146" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G147" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="H147" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="I147" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M147" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="I99" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="J99" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K99" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M99" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="N99" s="2" t="s">
-        <v>306</v>
+      <c r="N147" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I148" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M148" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="N148" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -6003,6 +8293,21 @@
     <hyperlink ref="L85" r:id="rId13"/>
     <hyperlink ref="L86" r:id="rId14"/>
     <hyperlink ref="L87" r:id="rId15"/>
+    <hyperlink ref="L101" r:id="rId16"/>
+    <hyperlink ref="L102" r:id="rId17"/>
+    <hyperlink ref="L110" r:id="rId18"/>
+    <hyperlink ref="L115" r:id="rId19"/>
+    <hyperlink ref="L116" r:id="rId20"/>
+    <hyperlink ref="L117" r:id="rId21"/>
+    <hyperlink ref="L120" r:id="rId22"/>
+    <hyperlink ref="L121" r:id="rId23"/>
+    <hyperlink ref="L122" r:id="rId24"/>
+    <hyperlink ref="L124" r:id="rId25"/>
+    <hyperlink ref="L125" r:id="rId26"/>
+    <hyperlink ref="L126" r:id="rId27"/>
+    <hyperlink ref="L134" r:id="rId28"/>
+    <hyperlink ref="L135" r:id="rId29"/>
+    <hyperlink ref="L136" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -6011,7 +8316,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6030,16 +8335,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6050,16 +8355,16 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6070,16 +8375,16 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6090,16 +8395,16 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6110,16 +8415,16 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6130,16 +8435,16 @@
         <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6150,16 +8455,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="D7" s="2">
         <v>627</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6170,16 +8475,16 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="D8" s="2">
         <v>60</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6190,16 +8495,16 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6210,16 +8515,16 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6230,16 +8535,16 @@
         <v>13</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6250,16 +8555,16 @@
         <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6270,16 +8575,16 @@
         <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="D13" s="2">
         <v>114</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6290,16 +8595,16 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6310,16 +8615,16 @@
         <v>13</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="D15" s="2">
         <v>12</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6330,16 +8635,16 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6350,16 +8655,16 @@
         <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6370,16 +8675,16 @@
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="D18" s="2">
         <v>137</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6390,16 +8695,16 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6410,16 +8715,16 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="D20" s="2">
         <v>1381</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6430,16 +8735,16 @@
         <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="D21" s="2">
         <v>1136</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6450,16 +8755,16 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="D22" s="2">
         <v>168</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6470,16 +8775,16 @@
         <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="D23" s="2">
         <v>7</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6490,16 +8795,16 @@
         <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="D24" s="2">
         <v>46</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6510,16 +8815,16 @@
         <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6530,16 +8835,16 @@
         <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6550,16 +8855,16 @@
         <v>18</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6570,16 +8875,16 @@
         <v>18</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6590,16 +8895,16 @@
         <v>18</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6610,16 +8915,16 @@
         <v>18</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="D30" s="2">
         <v>627</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6630,16 +8935,16 @@
         <v>18</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="D31" s="2">
         <v>60</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6650,16 +8955,16 @@
         <v>18</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6670,16 +8975,16 @@
         <v>18</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6690,16 +8995,16 @@
         <v>18</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6710,16 +9015,16 @@
         <v>18</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6730,16 +9035,16 @@
         <v>18</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="D36" s="2">
         <v>114</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6750,16 +9055,16 @@
         <v>18</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6770,16 +9075,16 @@
         <v>18</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="D38" s="2">
         <v>12</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6790,16 +9095,16 @@
         <v>18</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6810,16 +9115,16 @@
         <v>18</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6830,16 +9135,16 @@
         <v>18</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="D41" s="2">
         <v>137</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6850,16 +9155,476 @@
         <v>18</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1387</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1141</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D45" s="2">
+        <v>169</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D46" s="2">
+        <v>7</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D47" s="2">
+        <v>48</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D48" s="2">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D51" s="2">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D52" s="2">
+        <v>0</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D53" s="2">
+        <v>627</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D54" s="2">
+        <v>60</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D59" s="2">
+        <v>114</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D61" s="2">
+        <v>12</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D63" s="2">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D64" s="2">
+        <v>137</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
